--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -15,12 +15,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ \¥* #,##0.00_ ;_ \¥* -#,##0.00_ ;_ \¥* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ \¥* #,##0_ ;_ \¥* -#,##0_ ;_ \¥* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -599,7 +600,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -679,6 +680,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0"/>
@@ -1022,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -4018,6 +4028,68 @@
       </c>
       <c r="N46" s="21" t="n">
         <v>46276</v>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1" s="26">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B47" s="28" t="inlineStr">
+        <is>
+          <t>XOXOGossipGirlRichTeaRumors</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="inlineStr">
+        <is>
+          <t>绯闻女孩：八卦社交名流公司</t>
+        </is>
+      </c>
+      <c r="D47" s="28" t="inlineStr">
+        <is>
+          <t>JayESims</t>
+        </is>
+      </c>
+      <c r="E47" s="28" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/JayESims</t>
+        </is>
+      </c>
+      <c r="F47" s="28" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139755723</t>
+        </is>
+      </c>
+      <c r="G47" s="29" t="n">
+        <v>46279</v>
+      </c>
+      <c r="H47" s="29" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I47" s="27" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J47" s="27" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="inlineStr">
+        <is>
+          <t>images/jayesims-xoxogossipgirlrichtearumors.png</t>
+        </is>
+      </c>
+      <c r="L47" s="28" t="n"/>
+      <c r="M47" s="27" t="inlineStr">
+        <is>
+          <t>游戏玩法</t>
+        </is>
+      </c>
+      <c r="N47" s="29" t="n">
+        <v>46279</v>
       </c>
     </row>
   </sheetData>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -15,13 +15,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ \¥* #,##0.00_ ;_ \¥* -#,##0.00_ ;_ \¥* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ \¥* #,##0_ ;_ \¥* -#,##0_ ;_ \¥* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -4085,7 +4084,7 @@
       <c r="L47" s="28" t="n"/>
       <c r="M47" s="27" t="inlineStr">
         <is>
-          <t>游戏玩法</t>
+          <t>职业</t>
         </is>
       </c>
       <c r="N47" s="29" t="n">

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -3895,7 +3895,11 @@
           <t>images/jayesims-high-school-tea.png</t>
         </is>
       </c>
-      <c r="L44" s="13" t="inlineStr"/>
+      <c r="L44" s="13" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1ae-CgAvXYm47S6mnQZziCQ?pwd=a84u 提取码: a84u</t>
+        </is>
+      </c>
       <c r="M44" s="12" t="inlineStr">
         <is>
           <t>游戏玩法</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="G7" s="21" t="n">
-        <v>46225</v>
+        <v>46280</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>46225</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="G11" s="21" t="n">
-        <v>46216</v>
+        <v>46280</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>46216</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="G35" s="21" t="n">
-        <v>46255</v>
+        <v>46280</v>
       </c>
       <c r="H35" s="21" t="n">
         <v>46255</v>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G40" s="22" t="n">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="H40" s="22" t="n">
         <v>46265</v>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -15,12 +15,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ \¥* #,##0.00_ ;_ \¥* -#,##0.00_ ;_ \¥* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ \¥* #,##0_ ;_ \¥* -#,##0_ ;_ \¥* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -1031,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -4093,6 +4094,68 @@
       </c>
       <c r="N47" s="29" t="n">
         <v>46279</v>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1" s="26">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>PregnancyOverhaul_v1.2</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>怀孕大修</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>RBK</t>
+        </is>
+      </c>
+      <c r="E48" s="28" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/RealismByKatie</t>
+        </is>
+      </c>
+      <c r="F48" s="28" t="inlineStr">
+        <is>
+          <t>https://realismbykatie.com/pregnancy-overhaul/</t>
+        </is>
+      </c>
+      <c r="G48" s="29" t="n">
+        <v>46281</v>
+      </c>
+      <c r="H48" s="29" t="n">
+        <v>46281</v>
+      </c>
+      <c r="I48" s="27" t="inlineStr">
+        <is>
+          <t>Lot51 核心库、XML 注入器</t>
+        </is>
+      </c>
+      <c r="J48" s="27" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="K48" s="28" t="inlineStr">
+        <is>
+          <t>images/rbk-pregnancyoverhaul-v1-2.png</t>
+        </is>
+      </c>
+      <c r="L48" s="28" t="inlineStr"/>
+      <c r="M48" s="27" t="inlineStr">
+        <is>
+          <t>游戏玩法</t>
+        </is>
+      </c>
+      <c r="N48" s="29" t="n">
+        <v>46281</v>
       </c>
     </row>
   </sheetData>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -15,13 +15,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ \¥* #,##0.00_ ;_ \¥* -#,##0.00_ ;_ \¥* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ \¥* #,##0_ ;_ \¥* -#,##0_ ;_ \¥* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -1032,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -2610,22 +2609,22 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>MorningSicknessOverhaul_v1.0</t>
+          <t>LaundromatLotTrait_v.1.0.3</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>孕吐大修</t>
+          <t>自助付费洗衣房</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>RBK</t>
+          <t>Andirz</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>https://www.patreon.com/RealismByKatie</t>
+          <t>https://andirz.com/</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr"/>
@@ -2647,17 +2646,17 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>images/rbk-morningsicknessoverhaul-v1-0.png</t>
+          <t>images/andirz-laundromatlottrait-v-1-0-3.png</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1vXR7PbTSX7KI0RbKnI2_rQ 提取码: eahu</t>
+          <t>链接: https://pan.baidu.com/s/1lzsj3v43w5DpwuRHGcBsAg 提取码: xmcj</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>覆盖替换</t>
+          <t>用地特征</t>
         </is>
       </c>
       <c r="N25" s="21" t="n">
@@ -2672,22 +2671,22 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>LaundromatLotTrait_v.1.0.3</t>
+          <t>BrosGoneDeep</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>自助付费洗衣房</t>
+          <t>嘴上兄弟 实则不止</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Andirz</t>
+          <t>JayESims</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>https://andirz.com/</t>
+          <t>https://www.patreon.com/cw/JayESims</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr"/>
@@ -2699,7 +2698,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Lot51 核心库</t>
+          <t>XML 注入器</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -2709,17 +2708,17 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>images/andirz-laundromatlottrait-v-1-0-3.png</t>
+          <t>images/jayesims-brosgonedeep.png</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1lzsj3v43w5DpwuRHGcBsAg 提取码: xmcj</t>
+          <t>链接: https://pan.baidu.com/s/1Yp9oF66mxL4VTP3k-Y048g 提取码: p4aa</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>用地特征</t>
+          <t>游戏玩法</t>
         </is>
       </c>
       <c r="N26" s="21" t="n">
@@ -2734,58 +2733,62 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>BrosGoneDeep</t>
+          <t>PeoplePleaserTrait</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>嘴上兄弟 实则不止</t>
+          <t>讨好型人格</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>JayESims</t>
+          <t>Klimter</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>https://www.patreon.com/cw/JayESims</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr"/>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/people-pleaser-trait-klimter</t>
+        </is>
+      </c>
       <c r="G27" s="21" t="n">
-        <v>46203</v>
+        <v>46239</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>46203</v>
+        <v>46239</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>XML 注入器</t>
+          <t>无需前置</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>无需放第一层</t>
+          <t>必须放第一层</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>images/jayesims-brosgonedeep.png</t>
+          <t>images/klimter-peoplepleasertrait.png</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1Yp9oF66mxL4VTP3k-Y048g 提取码: p4aa</t>
+          <t>链接: https://pan.baidu.com/s/1nmXL7aEQpZvDmqirQ6obrA 提取码: 8p9p</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>游戏玩法</t>
+          <t>人物特征</t>
         </is>
       </c>
       <c r="N27" s="21" t="n">
-        <v>46203</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="28" ht="36" customFormat="1" customHeight="1" s="19">
@@ -2796,12 +2799,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>PeoplePleaserTrait</t>
+          <t>FestiveTrait</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>讨好型人格</t>
+          <t>节庆控</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -2816,14 +2819,14 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>https://www.curseforge.com/sims4/mods/people-pleaser-trait-klimter</t>
+          <t>https://www.curseforge.com/sims4/mods/festive-trait</t>
         </is>
       </c>
       <c r="G28" s="21" t="n">
-        <v>46239</v>
+        <v>46275</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
@@ -2837,12 +2840,12 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-peoplepleasertrait.png</t>
+          <t>images/klimter-festivetrait.png</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1nmXL7aEQpZvDmqirQ6obrA 提取码: 8p9p</t>
+          <t>链接: https://pan.baidu.com/s/16qbiUzhVnTx7oY3Du6uXEw 提取码: shrr</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
@@ -2851,7 +2854,7 @@
         </is>
       </c>
       <c r="N28" s="21" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="29" ht="36" customFormat="1" customHeight="1" s="19">
@@ -2862,12 +2865,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>FestiveTrait</t>
+          <t>MoreTeenTraits</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>节庆控</t>
+          <t>更多青少年特征</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -2880,16 +2883,16 @@
           <t>https://www.patreon.com/cw/klimter</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>https://www.curseforge.com/sims4/mods/festive-trait</t>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/more-teen-traits</t>
         </is>
       </c>
       <c r="G29" s="21" t="n">
-        <v>46275</v>
+        <v>46244</v>
       </c>
       <c r="H29" s="21" t="n">
-        <v>46248</v>
+        <v>46272</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
@@ -2903,12 +2906,12 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-festivetrait.png</t>
+          <t>images/klimter-moreteentraits.png</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/16qbiUzhVnTx7oY3Du6uXEw 提取码: shrr</t>
+          <t>链接: https://pan.baidu.com/s/1ws8BstJmKltWiMha-x3VWQ?pwd=x1qc 提取码: x1qc</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
@@ -2917,7 +2920,7 @@
         </is>
       </c>
       <c r="N29" s="21" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="30" ht="36" customFormat="1" customHeight="1" s="19">
@@ -2928,12 +2931,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>MoreTeenTraits</t>
+          <t>MoreSocialTraits</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>更多青少年特征</t>
+          <t>更多社交特征</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -2948,14 +2951,14 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>https://www.curseforge.com/sims4/mods/more-teen-traits</t>
+          <t>https://www.curseforge.com/sims4/mods/more-social-traits</t>
         </is>
       </c>
       <c r="G30" s="21" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>46272</v>
+        <v>46253</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
@@ -2969,12 +2972,12 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-moreteentraits.png</t>
+          <t>images/klimter-moresocialtraits.png</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1ws8BstJmKltWiMha-x3VWQ?pwd=x1qc 提取码: x1qc</t>
+          <t>链接: https://pan.baidu.com/s/1AnvJWTbMezMBEwV_NtulzQ 提取码: i92t</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -2983,7 +2986,7 @@
         </is>
       </c>
       <c r="N30" s="21" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="31" ht="36" customFormat="1" customHeight="1" s="19">
@@ -2994,12 +2997,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>MoreSocialTraits</t>
+          <t>MoreElderTraits</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>更多社交特征</t>
+          <t>更多老年特征</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -3014,14 +3017,14 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>https://www.curseforge.com/sims4/mods/more-social-traits</t>
+          <t>https://www.curseforge.com/sims4/mods/more-elder-traits</t>
         </is>
       </c>
       <c r="G31" s="21" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="H31" s="21" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
@@ -3035,12 +3038,12 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-moresocialtraits.png</t>
+          <t>images/klimter-moreeldertraits.png</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1AnvJWTbMezMBEwV_NtulzQ 提取码: i92t</t>
+          <t>链接: https://pan.baidu.com/s/1CFpOqmuLSkTAUyxnHHqTGQ 提取码: xbm8</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -3049,7 +3052,7 @@
         </is>
       </c>
       <c r="N31" s="21" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="32" ht="36" customFormat="1" customHeight="1" s="19">
@@ -3060,12 +3063,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>MoreElderTraits</t>
+          <t>FoolishTrait</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>更多老年特征</t>
+          <t>莽撞</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -3078,16 +3081,16 @@
           <t>https://www.patreon.com/cw/klimter</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>https://www.curseforge.com/sims4/mods/more-elder-traits</t>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/foolish-trait</t>
         </is>
       </c>
       <c r="G32" s="21" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
@@ -3101,12 +3104,12 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-moreeldertraits.png</t>
+          <t>images/klimter-foolishtrait.png</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1CFpOqmuLSkTAUyxnHHqTGQ 提取码: xbm8</t>
+          <t>链接: https://pan.baidu.com/s/16GDYoljTlJduDEoxwykyuQ 提取码: db2z</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
@@ -3115,7 +3118,7 @@
         </is>
       </c>
       <c r="N32" s="21" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="33" ht="36" customFormat="1" customHeight="1" s="19">
@@ -3126,12 +3129,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>FoolishTrait</t>
+          <t>ParentalTrait</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>莽撞</t>
+          <t>称职父母</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -3144,16 +3147,16 @@
           <t>https://www.patreon.com/cw/klimter</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>https://www.curseforge.com/sims4/mods/foolish-trait</t>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/parental-trait</t>
         </is>
       </c>
       <c r="G33" s="21" t="n">
-        <v>46250</v>
+        <v>46275</v>
       </c>
       <c r="H33" s="21" t="n">
-        <v>46250</v>
+        <v>46253</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
@@ -3167,12 +3170,12 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-foolishtrait.png</t>
+          <t>images/klimter-parentaltrait.png</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/16GDYoljTlJduDEoxwykyuQ 提取码: db2z</t>
+          <t>链接: https://pan.baidu.com/s/1vhK_sEwzqs7OF2afKNI2sg 提取码: 93p1</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -3181,7 +3184,7 @@
         </is>
       </c>
       <c r="N33" s="21" t="n">
-        <v>46250</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="34" ht="36" customFormat="1" customHeight="1" s="19">
@@ -3192,12 +3195,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>ParentalTrait</t>
+          <t>PlanetInspiredTraits</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>称职父母</t>
+          <t>行星之子</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -3212,14 +3215,14 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>https://www.curseforge.com/sims4/mods/parental-trait</t>
+          <t>https://www.curseforge.com/sims4/mods/planetary-traits</t>
         </is>
       </c>
       <c r="G34" s="21" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
@@ -3233,12 +3236,12 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-parentaltrait.png</t>
+          <t>images/klimter-planetinspiredtraits.png</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1vhK_sEwzqs7OF2afKNI2sg 提取码: 93p1</t>
+          <t>链接: https://pan.baidu.com/s/1Nb2iuFfmfMc4EKRCyP_0Rg 提取码: gn66</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -3247,7 +3250,7 @@
         </is>
       </c>
       <c r="N34" s="21" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="35" ht="36" customFormat="1" customHeight="1" s="19">
@@ -3258,12 +3261,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>PlanetInspiredTraits</t>
+          <t>BabyFeverTrait</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>行星之子</t>
+          <t>宝宝控</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -3278,14 +3281,14 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>https://www.curseforge.com/sims4/mods/planetary-traits</t>
+          <t>https://www.curseforge.com/sims4/mods/baby-fever-trait</t>
         </is>
       </c>
       <c r="G35" s="21" t="n">
-        <v>46280</v>
+        <v>46257</v>
       </c>
       <c r="H35" s="21" t="n">
-        <v>46255</v>
+        <v>46263</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
@@ -3299,12 +3302,12 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-planetinspiredtraits.png</t>
+          <t>images/klimter-babyfevertrait.png</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1Nb2iuFfmfMc4EKRCyP_0Rg 提取码: gn66</t>
+          <t>链接: https://pan.baidu.com/s/1S-SGWfxmI1jKhlEJo7YhqQ 提取码: qg5d</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
@@ -3313,7 +3316,7 @@
         </is>
       </c>
       <c r="N35" s="21" t="n">
-        <v>46255</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="36" ht="36" customFormat="1" customHeight="1" s="19">
@@ -3324,12 +3327,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>BabyFeverTrait</t>
+          <t>BrattyTrait</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>宝宝控</t>
+          <t>爱耍性子</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -3344,14 +3347,14 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>https://www.curseforge.com/sims4/mods/baby-fever-trait</t>
+          <t>https://www.curseforge.com/sims4/mods/bratty-trait</t>
         </is>
       </c>
       <c r="G36" s="21" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>46263</v>
+        <v>46267</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
@@ -3365,12 +3368,12 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-babyfevertrait.png</t>
+          <t>images/klimter-brattytrait.png</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1S-SGWfxmI1jKhlEJo7YhqQ 提取码: qg5d</t>
+          <t>链接: https://pan.baidu.com/s/1PYCaYeJXJ6ETFA-y9BT7_g 提取码: xa2k</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
@@ -3379,7 +3382,7 @@
         </is>
       </c>
       <c r="N36" s="21" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="37" ht="36" customFormat="1" customHeight="1" s="19">
@@ -3390,12 +3393,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>BrattyTrait</t>
+          <t>MoreHobbyTraits</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>爱耍性子</t>
+          <t>更多爱好特征</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -3410,14 +3413,14 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>https://www.curseforge.com/sims4/mods/bratty-trait</t>
+          <t>https://www.curseforge.com/sims4/mods/more-hobby-traits</t>
         </is>
       </c>
       <c r="G37" s="21" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H37" s="21" t="n">
-        <v>46267</v>
+        <v>46263</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -3431,12 +3434,12 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-brattytrait.png</t>
+          <t>images/klimter-morehobytraits.png</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1PYCaYeJXJ6ETFA-y9BT7_g 提取码: xa2k</t>
+          <t>链接: https://pan.baidu.com/s/1NyT9GWICVfyLzQvtpjexMQ 提取码: hqnw</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
@@ -3445,7 +3448,7 @@
         </is>
       </c>
       <c r="N37" s="21" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="38" ht="36" customFormat="1" customHeight="1" s="19">
@@ -3456,12 +3459,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>MoreHobbyTraits</t>
+          <t>Immortalitytrait</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>更多爱好特征</t>
+          <t>永不衰老</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -3474,16 +3477,16 @@
           <t>https://www.patreon.com/cw/klimter</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>https://www.curseforge.com/sims4/mods/more-hobby-traits</t>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/immortality-trait</t>
         </is>
       </c>
       <c r="G38" s="21" t="n">
         <v>46262</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
@@ -3497,12 +3500,12 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>images/klimter-morehobytraits.png</t>
+          <t>images/klimter-immortalitytrait.png</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1NyT9GWICVfyLzQvtpjexMQ 提取码: hqnw</t>
+          <t>链接: https://pan.baidu.com/s/11FRdiNPX3V_eWde9lEdBag 提取码: zfn6</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
@@ -3515,69 +3518,69 @@
       </c>
     </row>
     <row r="39" ht="36" customFormat="1" customHeight="1" s="19">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>已发布</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Immortalitytrait</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>永不衰老</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>MaliciousTrait</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>捣蛋鬼特征</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>Klimter</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>https://www.patreon.com/cw/klimter</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>https://www.curseforge.com/sims4/mods/immortality-trait</t>
-        </is>
-      </c>
-      <c r="G39" s="21" t="n">
-        <v>46262</v>
-      </c>
-      <c r="H39" s="21" t="n">
-        <v>46262</v>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/malicious-trait</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>46280</v>
+      </c>
+      <c r="H39" s="22" t="n">
+        <v>46265</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>无需前置</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>必须放第一层</t>
         </is>
       </c>
-      <c r="K39" s="6" t="inlineStr">
-        <is>
-          <t>images/klimter-immortalitytrait.png</t>
-        </is>
-      </c>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>链接: https://pan.baidu.com/s/11FRdiNPX3V_eWde9lEdBag 提取码: zfn6</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>images/klimter-malicioustrait.png</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/s/1_bbfDZKQ2sqebHS_p5zhCA?pwd=4m8g 提取码: 4m8g</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>
       </c>
-      <c r="N39" s="21" t="n">
-        <v>46262</v>
+      <c r="N39" s="22" t="n">
+        <v>46265</v>
       </c>
     </row>
     <row r="40" ht="36" customFormat="1" customHeight="1" s="19">
@@ -3588,12 +3591,12 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>MaliciousTrait</t>
+          <t>PatientTrait</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>捣蛋鬼特征</t>
+          <t>耐心</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -3608,14 +3611,14 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>https://www.curseforge.com/sims4/mods/malicious-trait</t>
+          <t>https://www.curseforge.com/sims4/mods/patient-trait</t>
         </is>
       </c>
       <c r="G40" s="22" t="n">
-        <v>46280</v>
+        <v>46267</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -3629,12 +3632,12 @@
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>images/klimter-malicioustrait.png</t>
+          <t>images/klimter-patienttrait.png</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>https://pan.baidu.com/s/1_bbfDZKQ2sqebHS_p5zhCA?pwd=4m8g 提取码: 4m8g</t>
+          <t>链接: https://pan.baidu.com/s/1PZsbfnQlKy-7P2uEkwN4gg?pwd=z4m9 提取码: z4m9</t>
         </is>
       </c>
       <c r="M40" s="9" t="inlineStr">
@@ -3643,7 +3646,7 @@
         </is>
       </c>
       <c r="N40" s="22" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="41" ht="36" customFormat="1" customHeight="1" s="19">
@@ -3654,12 +3657,12 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>PatientTrait</t>
+          <t>Soft-HeartedTrait</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>耐心</t>
+          <t>心肠软弱</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -3674,14 +3677,14 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>https://www.curseforge.com/sims4/mods/patient-trait</t>
+          <t>https://www.curseforge.com/sims4/mods/soft-hearted-trait</t>
         </is>
       </c>
       <c r="G41" s="22" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>46274</v>
+        <v>46269</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
@@ -3695,12 +3698,12 @@
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>images/klimter-patienttrait.png</t>
+          <t>images/klimter-softheartedtrait.png</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1PZsbfnQlKy-7P2uEkwN4gg?pwd=z4m9 提取码: z4m9</t>
+          <t>链接: https://pan.baidu.com/s/1IwpX1_AAlImKcdtIlp1Qgw?pwd=asba 提取码: asba</t>
         </is>
       </c>
       <c r="M41" s="9" t="inlineStr">
@@ -3709,73 +3712,73 @@
         </is>
       </c>
       <c r="N41" s="22" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="42" ht="36" customFormat="1" customHeight="1" s="19">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>已发布</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Soft-HeartedTrait</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>心肠软弱</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>TemptingTrait</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>勾引者</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Klimter</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>https://www.patreon.com/cw/klimter</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>https://www.curseforge.com/sims4/mods/soft-hearted-trait</t>
-        </is>
-      </c>
-      <c r="G42" s="22" t="n">
-        <v>46269</v>
-      </c>
-      <c r="H42" s="22" t="n">
-        <v>46269</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/tempting-trait</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="n">
+        <v>46275</v>
+      </c>
+      <c r="H42" s="24" t="n">
+        <v>46278</v>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>无需前置</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr">
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>必须放第一层</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t>images/klimter-softheartedtrait.png</t>
-        </is>
-      </c>
-      <c r="L42" s="10" t="inlineStr">
-        <is>
-          <t>链接: https://pan.baidu.com/s/1IwpX1_AAlImKcdtIlp1Qgw?pwd=asba 提取码: asba</t>
-        </is>
-      </c>
-      <c r="M42" s="9" t="inlineStr">
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>images/klimter-temptingtrait.png</t>
+        </is>
+      </c>
+      <c r="L42" s="13" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1ErMmagLQ17IYLLQqYOMZGQ?pwd=eugh 提取码: eugh</t>
+        </is>
+      </c>
+      <c r="M42" s="12" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>
       </c>
-      <c r="N42" s="22" t="n">
-        <v>46269</v>
+      <c r="N42" s="24" t="n">
+        <v>46271</v>
       </c>
     </row>
     <row r="43" ht="36" customFormat="1" customHeight="1" s="23">
@@ -3786,128 +3789,124 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>TemptingTrait</t>
+          <t>High School Tea</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>勾引者</t>
+          <t>高中吃瓜</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Klimter</t>
+          <t>JayESims</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>https://www.patreon.com/cw/klimter</t>
+          <t>https://www.patreon.com/cw/JayESims</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>https://www.curseforge.com/sims4/mods/tempting-trait</t>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139297180</t>
         </is>
       </c>
       <c r="G43" s="24" t="n">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>46278</v>
+        <v>46272</v>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>无需前置</t>
+          <t>XML 注入器</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>必须放第一层</t>
+          <t>无需放第一层</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>images/klimter-temptingtrait.png</t>
+          <t>images/jayesims-high-school-tea.png</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>链接: https://pan.baidu.com/s/1ErMmagLQ17IYLLQqYOMZGQ?pwd=eugh 提取码: eugh</t>
+          <t>链接: https://pan.baidu.com/s/1ae-CgAvXYm47S6mnQZziCQ?pwd=a84u 提取码: a84u</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
-          <t>人物特征</t>
+          <t>游戏玩法</t>
         </is>
       </c>
       <c r="N43" s="24" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="44" ht="36" customFormat="1" customHeight="1" s="23">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>已发布</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>High School Tea</t>
-        </is>
-      </c>
-      <c r="C44" s="13" t="inlineStr">
-        <is>
-          <t>高中吃瓜</t>
-        </is>
-      </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>If You’re Wondering If I Hate You… I Absolutely Do</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>别猜了 我恨你</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>JayESims</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>https://www.patreon.com/cw/JayESims</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
-        <is>
-          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139297180</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="n">
-        <v>46272</v>
-      </c>
-      <c r="H44" s="24" t="n">
-        <v>46272</v>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139743434</t>
+        </is>
+      </c>
+      <c r="G44" s="21" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H44" s="21" t="n">
+        <v>46274</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>XML 注入器</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>无需放第一层</t>
         </is>
       </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>images/jayesims-high-school-tea.png</t>
-        </is>
-      </c>
-      <c r="L44" s="13" t="inlineStr">
-        <is>
-          <t>链接: https://pan.baidu.com/s/1ae-CgAvXYm47S6mnQZziCQ?pwd=a84u 提取码: a84u</t>
-        </is>
-      </c>
-      <c r="M44" s="12" t="inlineStr">
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>images/jayesims-if-you-re-wondering-if-i-hate-you-i-absolutely-do.png</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr">
         <is>
           <t>游戏玩法</t>
         </is>
       </c>
-      <c r="N44" s="24" t="n">
-        <v>46272</v>
+      <c r="N44" s="21" t="n">
+        <v>46274</v>
       </c>
     </row>
     <row r="45" ht="36" customFormat="1" customHeight="1" s="25">
@@ -3918,12 +3917,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>If You’re Wondering If I Hate You… I Absolutely Do</t>
+          <t>Once Upon a Side Chick</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>别猜了 我恨你</t>
+          <t>从前有个小三</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -3938,14 +3937,14 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139743434</t>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139416119</t>
         </is>
       </c>
       <c r="G45" s="21" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H45" s="21" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
@@ -3959,79 +3958,79 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>images/jayesims-if-you-re-wondering-if-i-hate-you-i-absolutely-do.png</t>
+          <t>images/jayesims-once-upon-a-side-chick.png</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>游戏玩法</t>
+          <t>人物特征</t>
         </is>
       </c>
       <c r="N45" s="21" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1" s="26">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>已发布</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Once Upon a Side Chick</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>从前有个小三</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="inlineStr">
+        <is>
+          <t>XOXOGossipGirlRichTeaRumors</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="inlineStr">
+        <is>
+          <t>绯闻女孩：八卦社交名流公司</t>
+        </is>
+      </c>
+      <c r="D46" s="28" t="inlineStr">
         <is>
           <t>JayESims</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="28" t="inlineStr">
         <is>
           <t>https://www.patreon.com/cw/JayESims</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139416119</t>
-        </is>
-      </c>
-      <c r="G46" s="21" t="n">
-        <v>46276</v>
-      </c>
-      <c r="H46" s="21" t="n">
-        <v>46276</v>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="F46" s="28" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139755723</t>
+        </is>
+      </c>
+      <c r="G46" s="29" t="n">
+        <v>46279</v>
+      </c>
+      <c r="H46" s="29" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>XML 注入器</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="J46" s="27" t="inlineStr">
         <is>
           <t>无需放第一层</t>
         </is>
       </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>images/jayesims-once-upon-a-side-chick.png</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>人物特征</t>
-        </is>
-      </c>
-      <c r="N46" s="21" t="n">
-        <v>46276</v>
+      <c r="K46" s="28" t="inlineStr">
+        <is>
+          <t>images/jayesims-xoxogossipgirlrichtearumors.png</t>
+        </is>
+      </c>
+      <c r="L46" s="28" t="n"/>
+      <c r="M46" s="27" t="inlineStr">
+        <is>
+          <t>职业</t>
+        </is>
+      </c>
+      <c r="N46" s="29" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1" s="26">
@@ -4042,122 +4041,61 @@
       </c>
       <c r="B47" s="28" t="inlineStr">
         <is>
-          <t>XOXOGossipGirlRichTeaRumors</t>
+          <t>PregnancyOverhaul_v1.2</t>
         </is>
       </c>
       <c r="C47" s="28" t="inlineStr">
         <is>
-          <t>绯闻女孩：八卦社交名流公司</t>
+          <t>怀孕大修</t>
         </is>
       </c>
       <c r="D47" s="28" t="inlineStr">
         <is>
-          <t>JayESims</t>
+          <t>RBK</t>
         </is>
       </c>
       <c r="E47" s="28" t="inlineStr">
         <is>
-          <t>https://www.patreon.com/cw/JayESims</t>
+          <t>https://www.patreon.com/RealismByKatie</t>
         </is>
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139755723</t>
+          <t>https://realismbykatie.com/pregnancy-overhaul/</t>
         </is>
       </c>
       <c r="G47" s="29" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="H47" s="29" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="I47" s="27" t="inlineStr">
         <is>
-          <t>XML 注入器</t>
+          <t>Lot51 核心库、XML 注入器</t>
         </is>
       </c>
       <c r="J47" s="27" t="inlineStr">
         <is>
-          <t>无需放第一层</t>
+          <t>必须放第一层</t>
         </is>
       </c>
       <c r="K47" s="28" t="inlineStr">
         <is>
-          <t>images/jayesims-xoxogossipgirlrichtearumors.png</t>
-        </is>
-      </c>
-      <c r="L47" s="28" t="n"/>
+          <t>images/rbk-pregnancyoverhaul-v1-2.png</t>
+        </is>
+      </c>
+      <c r="L47" s="28" t="inlineStr"/>
       <c r="M47" s="27" t="inlineStr">
         <is>
-          <t>职业</t>
+          <t>游戏玩法</t>
         </is>
       </c>
       <c r="N47" s="29" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1" s="26">
-      <c r="A48" s="27" t="inlineStr">
-        <is>
-          <t>已发布</t>
-        </is>
-      </c>
-      <c r="B48" s="28" t="inlineStr">
-        <is>
-          <t>PregnancyOverhaul_v1.2</t>
-        </is>
-      </c>
-      <c r="C48" s="28" t="inlineStr">
-        <is>
-          <t>怀孕大修</t>
-        </is>
-      </c>
-      <c r="D48" s="28" t="inlineStr">
-        <is>
-          <t>RBK</t>
-        </is>
-      </c>
-      <c r="E48" s="28" t="inlineStr">
-        <is>
-          <t>https://www.patreon.com/RealismByKatie</t>
-        </is>
-      </c>
-      <c r="F48" s="28" t="inlineStr">
-        <is>
-          <t>https://realismbykatie.com/pregnancy-overhaul/</t>
-        </is>
-      </c>
-      <c r="G48" s="29" t="n">
         <v>46281</v>
       </c>
-      <c r="H48" s="29" t="n">
-        <v>46281</v>
-      </c>
-      <c r="I48" s="27" t="inlineStr">
-        <is>
-          <t>Lot51 核心库、XML 注入器</t>
-        </is>
-      </c>
-      <c r="J48" s="27" t="inlineStr">
-        <is>
-          <t>必须放第一层</t>
-        </is>
-      </c>
-      <c r="K48" s="28" t="inlineStr">
-        <is>
-          <t>images/rbk-pregnancyoverhaul-v1-2.png</t>
-        </is>
-      </c>
-      <c r="L48" s="28" t="inlineStr"/>
-      <c r="M48" s="27" t="inlineStr">
-        <is>
-          <t>游戏玩法</t>
-        </is>
-      </c>
-      <c r="N48" s="29" t="n">
-        <v>46281</v>
-      </c>
-    </row>
+    </row>
+    <row r="48" ht="36" customHeight="1" s="26"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" operator="between">

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -3899,7 +3899,11 @@
           <t>images/jayesims-if-you-re-wondering-if-i-hate-you-i-absolutely-do.png</t>
         </is>
       </c>
-      <c r="L44" s="6" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1fmAZJlziQoJjHMbqw7mRBA?pwd=d5zk 提取码: d5zk</t>
+        </is>
+      </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
           <t>游戏玩法</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -11,13 +11,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ \¥* #,##0.00_ ;_ \¥* -#,##0.00_ ;_ \¥* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ \¥* #,##0_ ;_ \¥* -#,##0_ ;_ \¥* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -4137,7 +4136,7 @@
       <c r="L48" s="6" t="n"/>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>游戏玩法</t>
+          <t>人物特征</t>
         </is>
       </c>
       <c r="N48" s="21" t="n">

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -3947,7 +3947,11 @@
           <t>images/jayesims-once-upon-a-side-chick.png</t>
         </is>
       </c>
-      <c r="L45" s="6" t="n"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/100FQWJ-yNtzyxHwsQqh9Kw?pwd=dhxg 提取码: dhxg</t>
+        </is>
+      </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -4145,6 +4145,192 @@
       </c>
       <c r="N48" s="21" t="n">
         <v>46283</v>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1" s="26">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Make It Clap</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>屁股摇起来</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>JayESims</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/JayESims</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139155476</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="n">
+        <v>46286</v>
+      </c>
+      <c r="H49" s="21" t="n">
+        <v>46286</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>images/jayesims-make-it-clap.png</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="n"/>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>用地特征</t>
+        </is>
+      </c>
+      <c r="N49" s="21" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1" s="26">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Can't Buy Love v2</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>花钱买爱情</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>WICKED PIXXEL</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>https://wickedpixxel.com/</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/wickedpixxel/posts/cant-buy-love-v2-168827831</t>
+        </is>
+      </c>
+      <c r="G50" s="21" t="n">
+        <v>46288</v>
+      </c>
+      <c r="H50" s="21" t="n">
+        <v>46288</v>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>images/wicked-pixxel-can-t-buy-love-v2.png</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="n"/>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>游戏玩法</t>
+        </is>
+      </c>
+      <c r="N50" s="21" t="n">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1" s="26">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>CameFromGenerationalMoney</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>含着金汤匙</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>JayESims</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/JayESims</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-140063827</t>
+        </is>
+      </c>
+      <c r="G51" s="21" t="n">
+        <v>46290</v>
+      </c>
+      <c r="H51" s="21" t="n">
+        <v>46290</v>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>images/jayesims-camefromgenerationalmoney.png</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="n"/>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N51" s="21" t="n">
+        <v>46290</v>
       </c>
     </row>
   </sheetData>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -3996,7 +3996,7 @@
         <v>46279</v>
       </c>
       <c r="H46" s="29" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="I46" s="27" t="inlineStr">
         <is>
@@ -4013,7 +4013,11 @@
           <t>images/jayesims-xoxogossipgirlrichtearumors.png</t>
         </is>
       </c>
-      <c r="L46" s="28" t="n"/>
+      <c r="L46" s="28" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1ZhUF2G65f2pw99h-YVr11Q?pwd=c7n2 提取码: c7n2</t>
+        </is>
+      </c>
       <c r="M46" s="27" t="inlineStr">
         <is>
           <t>职业</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4079,7 +4079,11 @@
           <t>images/rbk-pregnancyoverhaul-v1-2.png</t>
         </is>
       </c>
-      <c r="L47" s="28" t="n"/>
+      <c r="L47" s="28" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/12QzyVoX5CQqokJvIWovWiA?pwd=ayf2 提取码: ayf2</t>
+        </is>
+      </c>
       <c r="M47" s="27" t="inlineStr">
         <is>
           <t>游戏玩法</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4062,7 +4062,7 @@
         <v>46281</v>
       </c>
       <c r="H47" s="29" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="I47" s="27" t="inlineStr">
         <is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4128,7 +4128,7 @@
         <v>46283</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
@@ -4145,7 +4145,11 @@
           <t>images/jayesims-lovesbeingsingle.png</t>
         </is>
       </c>
-      <c r="L48" s="6" t="n"/>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1xHIzcEIhAcrNPY3RxYqgeA?pwd=jken 提取码: jken</t>
+        </is>
+      </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -4343,6 +4343,192 @@
       </c>
       <c r="N51" s="21" t="n">
         <v>46290</v>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1" s="26">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>The Luxury Estate Lot Trait Mod</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>豪华庄园</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>JayESims</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/JayESims</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-140290340</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="H52" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>images/jayesims-the-luxury-estate-lot-trait-mod.png</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="n"/>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>用地特征</t>
+        </is>
+      </c>
+      <c r="N52" s="21" t="n">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1" s="26">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Death by Childbirth_CF</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>分娩致死</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>AvathePit</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/pitsimmer</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/death-by-childbirth</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H53" s="21" t="n">
+        <v>46295</v>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Lot51 核心库</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>images/avathepit-death-by-childbirth-cf.png</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="n"/>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>游戏玩法</t>
+        </is>
+      </c>
+      <c r="N53" s="21" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1" s="26">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>The Sneaky Link Energy</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>地下情人</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>JayESims</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/JayESims</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139144216</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="n">
+        <v>46297</v>
+      </c>
+      <c r="H54" s="21" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>images/jayesims-the-sneaky-link-energy.png</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="n"/>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N54" s="21" t="n">
+        <v>46297</v>
       </c>
     </row>
   </sheetData>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4194,7 +4194,7 @@
         <v>46286</v>
       </c>
       <c r="H49" s="21" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -4211,7 +4211,11 @@
           <t>images/jayesims-make-it-clap.png</t>
         </is>
       </c>
-      <c r="L49" s="6" t="n"/>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1vxdLTiiA57IFd3BzW3uwyQ?pwd=2uif 提取码: 2uif</t>
+        </is>
+      </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
           <t>用地特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -2485,7 +2485,11 @@
           <t>https://www.patreon.com/cw/JayESims</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-158380859</t>
+        </is>
+      </c>
       <c r="G23" s="21" t="n">
         <v>46203</v>
       </c>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4264,7 +4264,7 @@
         <v>46288</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
@@ -4281,7 +4281,11 @@
           <t>images/wicked-pixxel-can-t-buy-love-v2.png</t>
         </is>
       </c>
-      <c r="L50" s="6" t="n"/>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1ysBWc2ZqD6cv9BjQd-KZgw?pwd=icrw 提取码: icrw</t>
+        </is>
+      </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
           <t>游戏玩法</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -11,12 +11,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_ \¥* #,##0.00_ ;_ \¥* -#,##0.00_ ;_ \¥* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_ \¥* #,##0_ ;_ \¥* -#,##0_ ;_ \¥* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ \¥* #,##0.00_ ;_ \¥* -#,##0.00_ ;_ \¥* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="169" formatCode="_ \¥* #,##0_ ;_ \¥* -#,##0_ ;_ \¥* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -159,7 +160,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -334,6 +335,12 @@
         <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F3EA"/>
+        <bgColor rgb="FFF7F3EA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border/>
@@ -436,19 +443,19 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="7" fillId="4" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="7" fillId="4" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="7" fillId="4" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="4" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1">
@@ -582,7 +589,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -669,6 +676,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1013,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -4541,6 +4557,192 @@
       </c>
       <c r="N54" s="21" t="n">
         <v>46297</v>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1" s="26">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>PSO_PurchaseMedicine_v.4.2.3</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
+        <is>
+          <t>购买药品</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="inlineStr">
+        <is>
+          <t>Andirz</t>
+        </is>
+      </c>
+      <c r="E55" s="28" t="inlineStr">
+        <is>
+          <t>https://andirz.com/</t>
+        </is>
+      </c>
+      <c r="F55" s="28" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/purchase-medicine</t>
+        </is>
+      </c>
+      <c r="G55" s="29" t="n">
+        <v>46300</v>
+      </c>
+      <c r="H55" s="29" t="n">
+        <v>46300</v>
+      </c>
+      <c r="I55" s="27" t="inlineStr">
+        <is>
+          <t>智能核心脚本、P.S.O 通用套装</t>
+        </is>
+      </c>
+      <c r="J55" s="27" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
+        <is>
+          <t>images/andirz-pso-purchasemedicine-v-4-2-3.png</t>
+        </is>
+      </c>
+      <c r="L55" s="28" t="n"/>
+      <c r="M55" s="27" t="inlineStr">
+        <is>
+          <t>游戏玩法</t>
+        </is>
+      </c>
+      <c r="N55" s="29" t="n">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1" s="26">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>Dark Emotions Trait v2</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
+        <is>
+          <t>黑暗情绪</t>
+        </is>
+      </c>
+      <c r="D56" s="28" t="inlineStr">
+        <is>
+          <t>WICKED PIXXEL</t>
+        </is>
+      </c>
+      <c r="E56" s="28" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/wickedpixxel</t>
+        </is>
+      </c>
+      <c r="F56" s="28" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/wickedpixxel/posts/dark-emotions-v2-169430175</t>
+        </is>
+      </c>
+      <c r="G56" s="29" t="n">
+        <v>46302</v>
+      </c>
+      <c r="H56" s="29" t="n">
+        <v>46302</v>
+      </c>
+      <c r="I56" s="27" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J56" s="27" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="inlineStr">
+        <is>
+          <t>images/wicked-pixxel-dark-emotions-trait-v2.png</t>
+        </is>
+      </c>
+      <c r="L56" s="28" t="n"/>
+      <c r="M56" s="27" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N56" s="29" t="n">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1" s="26">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>PSO_SimSimOnlineStore_v.5.7.0</t>
+        </is>
+      </c>
+      <c r="C57" s="28" t="inlineStr">
+        <is>
+          <t>SimSim 在线商店</t>
+        </is>
+      </c>
+      <c r="D57" s="28" t="inlineStr">
+        <is>
+          <t>Andirz</t>
+        </is>
+      </c>
+      <c r="E57" s="28" t="inlineStr">
+        <is>
+          <t>https://andirz.com/</t>
+        </is>
+      </c>
+      <c r="F57" s="28" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/simsim-online-store</t>
+        </is>
+      </c>
+      <c r="G57" s="29" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H57" s="29" t="n">
+        <v>46304</v>
+      </c>
+      <c r="I57" s="27" t="inlineStr">
+        <is>
+          <t>智能核心脚本、P.S.O 通用套装</t>
+        </is>
+      </c>
+      <c r="J57" s="27" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="inlineStr">
+        <is>
+          <t>images/andirz-pso-simsimonlinestore-v-5-7-0.png</t>
+        </is>
+      </c>
+      <c r="L57" s="28" t="n"/>
+      <c r="M57" s="27" t="inlineStr">
+        <is>
+          <t>游戏玩法</t>
+        </is>
+      </c>
+      <c r="N57" s="29" t="n">
+        <v>46304</v>
       </c>
     </row>
   </sheetData>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4567,7 +4567,7 @@
       </c>
       <c r="B55" s="28" t="inlineStr">
         <is>
-          <t>PSO_PurchaseMedicine_v.4.2.3</t>
+          <t>PSO_PurchaseMedicine_v.4.3.0</t>
         </is>
       </c>
       <c r="C55" s="28" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="K55" s="28" t="inlineStr">
         <is>
-          <t>images/andirz-pso-purchasemedicine-v-4-2-3.png</t>
+          <t>images/andirz-pso-purchasemedicine-v-4-3-0.png</t>
         </is>
       </c>
       <c r="L55" s="28" t="n"/>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1152,7 +1152,7 @@
         <v>46237</v>
       </c>
       <c r="H2" s="21" t="n">
-        <v>46268</v>
+        <v>46295</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>46281</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>46230</v>
+        <v>46295</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46278</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>46227</v>
+        <v>46295</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>46281</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>46225</v>
+        <v>46295</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>46281</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>46263</v>
+        <v>46295</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>46281</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>46216</v>
+        <v>46295</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46275</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>46209</v>
+        <v>46295</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>46239</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>46239</v>
+        <v>46295</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>46275</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>46248</v>
+        <v>46295</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>46244</v>
       </c>
       <c r="H29" s="21" t="n">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>46281</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>46253</v>
+        <v>46295</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>46281</v>
       </c>
       <c r="H31" s="21" t="n">
-        <v>46255</v>
+        <v>46295</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>46250</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>46250</v>
+        <v>46295</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>46275</v>
       </c>
       <c r="H33" s="21" t="n">
-        <v>46253</v>
+        <v>46295</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46281</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>46255</v>
+        <v>46295</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>46257</v>
       </c>
       <c r="H35" s="21" t="n">
-        <v>46263</v>
+        <v>46295</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>46260</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>46262</v>
       </c>
       <c r="H37" s="21" t="n">
-        <v>46263</v>
+        <v>46295</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46262</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>46262</v>
+        <v>46295</v>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>46281</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>46267</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>46274</v>
+        <v>46295</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>46269</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>46269</v>
+        <v>46295</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>46275</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>46278</v>
+        <v>46295</v>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>46272</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>46274</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>46274</v>
+        <v>46295</v>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>46276</v>
       </c>
       <c r="H45" s="21" t="n">
-        <v>46276</v>
+        <v>46295</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>46279</v>
       </c>
       <c r="H46" s="29" t="n">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="I46" s="27" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>46281</v>
       </c>
       <c r="H47" s="29" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="I47" s="27" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46283</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>46286</v>
       </c>
       <c r="H49" s="21" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>46290</v>
       </c>
       <c r="H51" s="21" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>46293</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>46297</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46300</v>
       </c>
       <c r="H55" s="29" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="I55" s="27" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>46302</v>
       </c>
       <c r="H56" s="29" t="n">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="I56" s="27" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>46304</v>
       </c>
       <c r="H57" s="29" t="n">
-        <v>46304</v>
+        <v>46295</v>
       </c>
       <c r="I57" s="27" t="inlineStr">
         <is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="G2" s="21" t="n">
-        <v>46237</v>
+        <v>46295</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>46295</v>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Aristocracy, Royalty, and Mistress Careers_4.9.2</t>
+          <t>Aristocracy, Royalty, and Mistress Careers_4.9.2.4</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>images/avathepit-aristocracy-royalty-and-mistress-careers-4-9-2.png</t>
+          <t>images/avathepit-aristocracy-royalty-and-mistress-careers-4-9-2-4.png</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4346,7 +4346,7 @@
         <v>46290</v>
       </c>
       <c r="H51" s="21" t="n">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
@@ -4363,7 +4363,11 @@
           <t>images/jayesims-camefromgenerationalmoney.png</t>
         </is>
       </c>
-      <c r="L51" s="6" t="n"/>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1huIxBET9d2LeebxSK1kVlA?pwd=8gf6 提取码: 8gf6</t>
+        </is>
+      </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
           <t>人物特征</t>
@@ -4408,7 +4412,7 @@
         <v>46293</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
@@ -4425,7 +4429,11 @@
           <t>images/jayesims-the-luxury-estate-lot-trait-mod.png</t>
         </is>
       </c>
-      <c r="L52" s="6" t="n"/>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1mXxcBcLge8PlU9Yga2hguQ?pwd=peqa 提取码: peqa</t>
+        </is>
+      </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
           <t>用地特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4478,7 +4478,7 @@
         <v>46295</v>
       </c>
       <c r="H53" s="21" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
@@ -4495,7 +4495,11 @@
           <t>images/avathepit-death-by-childbirth-cf.png</t>
         </is>
       </c>
-      <c r="L53" s="6" t="n"/>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1H13eMck55n70MHI1-TKMDw?pwd=2mgn 提取码: 2mgn</t>
+        </is>
+      </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
           <t>游戏玩法</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="G2" s="21" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>46295</v>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Aristocracy, Royalty, and Mistress Careers_4.9.2.4</t>
+          <t>Aristocracy, Royalty, and Mistress Careers_4.9.5</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>images/avathepit-aristocracy-royalty-and-mistress-careers-4-9-2-4.png</t>
+          <t>images/avathepit-aristocracy-royalty-and-mistress-careers-4-9-5.png</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4544,7 +4544,7 @@
         <v>46297</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
@@ -4561,7 +4561,11 @@
           <t>images/jayesims-the-sneaky-link-energy.png</t>
         </is>
       </c>
-      <c r="L54" s="6" t="n"/>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1vzsXNCGy9sj39MqWs-m0Hw?pwd=m6ar 提取码: m6ar</t>
+        </is>
+      </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -4759,6 +4759,192 @@
       </c>
       <c r="N57" s="29" t="n">
         <v>46304</v>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1" s="26">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>Romantic Tease V2</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>撩人精</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>WICKED PIXXEL</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>https://wickedpixxel.com/</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/wickedpixxel/posts/romantic-tease-134873590</t>
+        </is>
+      </c>
+      <c r="G58" s="24" t="n">
+        <v>46307</v>
+      </c>
+      <c r="H58" s="24" t="n">
+        <v>46307</v>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J58" s="12" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>images/wicked-pixxel-romantic-tease-v2.png</t>
+        </is>
+      </c>
+      <c r="L58" s="13" t="n"/>
+      <c r="M58" s="12" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N58" s="24" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1" s="26">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>JudgmentalTrait</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>评头论足</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/jugdemental-trait</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="n">
+        <v>46309</v>
+      </c>
+      <c r="H59" s="24" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="J59" s="12" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>images/klimter-judgmentaltrait.png</t>
+        </is>
+      </c>
+      <c r="L59" s="13" t="n"/>
+      <c r="M59" s="12" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N59" s="24" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1" s="26">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>Exquisite Taste Trait v2</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>极致品味</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>WICKED PIXXEL</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>https://wickedpixxel.com/</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/wickedpixxel/posts/exquisite-taste-169676696</t>
+        </is>
+      </c>
+      <c r="G60" s="24" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H60" s="24" t="n">
+        <v>46311</v>
+      </c>
+      <c r="I60" s="12" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>images/wicked-pixxel-exquisite-taste-trait-v2.png</t>
+        </is>
+      </c>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="12" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N60" s="24" t="n">
+        <v>46311</v>
       </c>
     </row>
   </sheetData>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4610,7 +4610,7 @@
         <v>46300</v>
       </c>
       <c r="H55" s="29" t="n">
-        <v>46295</v>
+        <v>46307</v>
       </c>
       <c r="I55" s="27" t="inlineStr">
         <is>
@@ -4627,7 +4627,11 @@
           <t>images/andirz-pso-purchasemedicine-v-4-3-0.png</t>
         </is>
       </c>
-      <c r="L55" s="28" t="n"/>
+      <c r="L55" s="28" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1VPmfGcr9l20TqE6yAO2flQ?pwd=bgd6 提取码: bgd6</t>
+        </is>
+      </c>
       <c r="M55" s="27" t="inlineStr">
         <is>
           <t>游戏玩法</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="G2" s="21" t="n">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="H2" s="21" t="n">
-        <v>46295</v>
+        <v>46307</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Aristocracy, Royalty, and Mistress Careers_4.9.5</t>
+          <t>Aristocracy, Royalty, and Mistress Careers_4.9.6</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>images/avathepit-aristocracy-royalty-and-mistress-careers-4-9-5.png</t>
+          <t>images/avathepit-aristocracy-royalty-and-mistress-careers-4-9-6.png</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4676,7 +4676,7 @@
         <v>46302</v>
       </c>
       <c r="H56" s="29" t="n">
-        <v>46295</v>
+        <v>46309</v>
       </c>
       <c r="I56" s="27" t="inlineStr">
         <is>
@@ -4693,7 +4693,11 @@
           <t>images/wicked-pixxel-dark-emotions-trait-v2.png</t>
         </is>
       </c>
-      <c r="L56" s="28" t="n"/>
+      <c r="L56" s="28" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1D8VTKA-5FKmcpHmStNFMiQ?pwd=u4g8 提取码: u4g8</t>
+        </is>
+      </c>
       <c r="M56" s="27" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4742,7 +4742,7 @@
         <v>46304</v>
       </c>
       <c r="H57" s="29" t="n">
-        <v>46295</v>
+        <v>46311</v>
       </c>
       <c r="I57" s="27" t="inlineStr">
         <is>
@@ -4759,7 +4759,11 @@
           <t>images/andirz-pso-simsimonlinestore-v-5-7-0.png</t>
         </is>
       </c>
-      <c r="L57" s="28" t="n"/>
+      <c r="L57" s="28" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1V5hst800m2V91bjFfSvlgw?pwd=ef24 提取码: ef24</t>
+        </is>
+      </c>
       <c r="M57" s="27" t="inlineStr">
         <is>
           <t>游戏玩法</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -4957,6 +4957,192 @@
       </c>
       <c r="N60" s="24" t="n">
         <v>46311</v>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1" s="26">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Peaceful v2</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>调停者</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>WICKED PIXXEL</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>https://wickedpixxel.com/</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/wickedpixxel/posts/peaceful-v2-170147817</t>
+        </is>
+      </c>
+      <c r="G61" s="21" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H61" s="21" t="n">
+        <v>46314</v>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>images/wicked-pixxel-peaceful-v2.png</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N61" s="21" t="n">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1" s="26">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Functional Lash Bar V3</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>功能性睫毛吧</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>WICKED PIXXEL</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>https://wickedpixxel.com/</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/wickedpixxel/posts/functional-lash-118921493</t>
+        </is>
+      </c>
+      <c r="G62" s="21" t="n">
+        <v>46316</v>
+      </c>
+      <c r="H62" s="21" t="n">
+        <v>46316</v>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>images/wicked-pixxel-functional-lash-bar-v3.png</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>游戏玩法</t>
+        </is>
+      </c>
+      <c r="N62" s="21" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1" s="26">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Certified BBC</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>定海神针认证</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>JayESims</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/JayESims</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-140371126</t>
+        </is>
+      </c>
+      <c r="G63" s="21" t="n">
+        <v>46318</v>
+      </c>
+      <c r="H63" s="21" t="n">
+        <v>46318</v>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>images/jayesims-certified-bbc.png</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr"/>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N63" s="21" t="n">
+        <v>46318</v>
       </c>
     </row>
   </sheetData>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4808,7 +4808,7 @@
         <v>46307</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
@@ -4825,7 +4825,11 @@
           <t>images/wicked-pixxel-romantic-tease-v2.png</t>
         </is>
       </c>
-      <c r="L58" s="13" t="n"/>
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1xPrWXpPBTXpBUgILwO8j4w?pwd=5mya 提取码: 5mya</t>
+        </is>
+      </c>
       <c r="M58" s="12" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4874,7 +4874,7 @@
         <v>46309</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
@@ -4891,7 +4891,11 @@
           <t>images/klimter-judgmentaltrait.png</t>
         </is>
       </c>
-      <c r="L59" s="13" t="n"/>
+      <c r="L59" s="13" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/12qvw_5Yh9d0nFYKi02eldw?pwd=xd6f 提取码: xd6f</t>
+        </is>
+      </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4940,7 +4940,7 @@
         <v>46311</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
@@ -4957,7 +4957,11 @@
           <t>images/wicked-pixxel-exquisite-taste-trait-v2.png</t>
         </is>
       </c>
-      <c r="L60" s="13" t="n"/>
+      <c r="L60" s="13" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1XZseR4y4HV1Klm2XMZVzBg?pwd=qgc4 提取码: qgc4</t>
+        </is>
+      </c>
       <c r="M60" s="12" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -5155,6 +5155,192 @@
       </c>
       <c r="N63" s="21" t="n">
         <v>46318</v>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1" s="26">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Forgetful v2</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>健忘者</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>WICKED PIXXEL</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>https://wickedpixxel.com/</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/wickedpixxel/posts/forgetful-v2-170148141</t>
+        </is>
+      </c>
+      <c r="G64" s="21" t="n">
+        <v>46321</v>
+      </c>
+      <c r="H64" s="21" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>images/wicked-pixxel-forgetful-v2.png</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr"/>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N64" s="21" t="n">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="65" ht="36" customHeight="1" s="26">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Our Sims, Our Stories Part 1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>我们的故事1</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>JayESims</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/JayESims</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-140243315</t>
+        </is>
+      </c>
+      <c r="G65" s="21" t="n">
+        <v>46323</v>
+      </c>
+      <c r="H65" s="21" t="n">
+        <v>46323</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>images/jayesims-our-sims-our-stories-part-1.png</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N65" s="21" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="66" ht="36" customHeight="1" s="26">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>We Can’t Be Friends 2</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>我们做不成朋友2</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>JayESims</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/JayESims</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139895564</t>
+        </is>
+      </c>
+      <c r="G66" s="21" t="n">
+        <v>46325</v>
+      </c>
+      <c r="H66" s="21" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>images/jayesims-we-cant-be-friends-2.png</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr"/>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>游戏玩法</t>
+        </is>
+      </c>
+      <c r="N66" s="21" t="n">
+        <v>46325</v>
       </c>
     </row>
   </sheetData>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -5006,7 +5006,7 @@
         <v>46314</v>
       </c>
       <c r="H61" s="21" t="n">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
@@ -5023,7 +5023,11 @@
           <t>images/wicked-pixxel-peaceful-v2.png</t>
         </is>
       </c>
-      <c r="L61" s="6" t="inlineStr"/>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1b8_cT2VVVhXWQWehRP8wdg?pwd=v7ey 提取码: v7ey</t>
+        </is>
+      </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -5345,6 +5345,68 @@
       </c>
       <c r="N66" s="21" t="n">
         <v>46325</v>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1" s="26">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Halloween Trick Or Treat Mod Collection</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>万圣节不给糖就捣蛋合集</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>WICKED PIXXEL</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>https://wickedpixxel.com/</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/wickedpixxel/posts/halloween-trick-173149467</t>
+        </is>
+      </c>
+      <c r="G67" s="21" t="n">
+        <v>46326</v>
+      </c>
+      <c r="H67" s="21" t="n">
+        <v>46326</v>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>images/wicked-pixxel-halloween-trick-or-treat-mod-collection.png</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>游戏玩法</t>
+        </is>
+      </c>
+      <c r="N67" s="21" t="n">
+        <v>46326</v>
       </c>
     </row>
   </sheetData>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -5072,7 +5072,7 @@
         <v>46316</v>
       </c>
       <c r="H62" s="21" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
@@ -5089,7 +5089,11 @@
           <t>images/wicked-pixxel-functional-lash-bar-v3.png</t>
         </is>
       </c>
-      <c r="L62" s="6" t="inlineStr"/>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1Qi5KZetr5WZQ27QJrG_s_A?pwd=5ac2 提取码: 5ac2</t>
+        </is>
+      </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
           <t>游戏玩法</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -5138,7 +5138,7 @@
         <v>46318</v>
       </c>
       <c r="H63" s="21" t="n">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
@@ -5155,7 +5155,11 @@
           <t>images/jayesims-certified-bbc.png</t>
         </is>
       </c>
-      <c r="L63" s="6" t="inlineStr"/>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1dRIIuxy-f7R9F_J1xN7RSQ?pwd=tbae 提取码: tbae</t>
+        </is>
+      </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="1"/>
@@ -5415,6 +5415,192 @@
       </c>
       <c r="N67" s="21" t="n">
         <v>46326</v>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1" s="26">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Deep Sleeper V2</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>深度睡眠者</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>WICKED PIXXEL</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>https://wickedpixxel.com/</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/wickedpixxel/posts/deep-sleeper-105855333</t>
+        </is>
+      </c>
+      <c r="G68" s="21" t="n">
+        <v>46328</v>
+      </c>
+      <c r="H68" s="21" t="n">
+        <v>46328</v>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>images/wicked-pixxel-deep-sleeper-v2.png</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr"/>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N68" s="21" t="n">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1" s="26">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Periodt</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>来例假了</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>JayESims</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/JayESims</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-140395494</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="n">
+        <v>46330</v>
+      </c>
+      <c r="H69" s="21" t="n">
+        <v>46330</v>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>images/jayesims-periodt.png</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr"/>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N69" s="21" t="n">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="70" ht="36" customHeight="1" s="26">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>LoveBomberTrait</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>先甜后渣</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>klimter</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/love-bomber-trait</t>
+        </is>
+      </c>
+      <c r="G70" s="21" t="n">
+        <v>46332</v>
+      </c>
+      <c r="H70" s="21" t="n">
+        <v>46332</v>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>images/klimter-lovebombertrait.png</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr"/>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+      <c r="N70" s="21" t="n">
+        <v>46332</v>
       </c>
     </row>
   </sheetData>
